--- a/artfynd/A 26322-2024 artfynd.xlsx
+++ b/artfynd/A 26322-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>104441791</v>
       </c>
       <c r="B2" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543066.3398502299</v>
+        <v>543067</v>
       </c>
       <c r="R2" t="n">
-        <v>7018113.379659214</v>
+        <v>7018113</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-07-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,6 +786,204 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>110398669</v>
+      </c>
+      <c r="B3" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ammerberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>542973</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7018234</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Louise Almén</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Louise Almén</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>110398668</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ammerberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>542928</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7018244</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Louise Almén</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Louise Almén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26322-2024 artfynd.xlsx
+++ b/artfynd/A 26322-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104441791</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110398669</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,8 +999,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110398668</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>